--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Back_Summary.xlsx
@@ -413,410 +413,1291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Measured by operator 7 on tool HRM-2</t>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Pad Pos 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>18.11722</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.38236</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17.7408</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.75472</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05368</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.99783</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.68706</v>
+        <v>17.8421</v>
       </c>
       <c r="D3" t="n">
-        <v>17.50943</v>
+        <v>17.35693</v>
       </c>
       <c r="E3" t="n">
-        <v>17.80478</v>
+        <v>17.52061</v>
       </c>
       <c r="F3" t="n">
-        <v>44.81634</v>
+        <v>45.81949</v>
       </c>
       <c r="G3" t="n">
         <v>0.05362</v>
       </c>
       <c r="H3" t="n">
-        <v>1.96036</v>
+        <v>1.92423</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.86372</v>
+        <v>17.96161</v>
       </c>
       <c r="D4" t="n">
-        <v>17.68774</v>
+        <v>17.28725</v>
       </c>
       <c r="E4" t="n">
-        <v>17.7448</v>
+        <v>17.59761</v>
       </c>
       <c r="F4" t="n">
-        <v>44.88025</v>
+        <v>45.11839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05303</v>
+        <v>0.0533</v>
       </c>
       <c r="H4" t="n">
-        <v>1.94034</v>
+        <v>1.94219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.90975</v>
+        <v>18.21259</v>
       </c>
       <c r="D5" t="n">
-        <v>17.49841</v>
+        <v>17.25712</v>
       </c>
       <c r="E5" t="n">
-        <v>17.24332</v>
+        <v>18.14119</v>
       </c>
       <c r="F5" t="n">
-        <v>44.20478</v>
+        <v>45.11773</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05344</v>
+        <v>0.0535</v>
       </c>
       <c r="H5" t="n">
-        <v>1.95774</v>
+        <v>1.91664</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.90762</v>
+        <v>17.83426</v>
       </c>
       <c r="D6" t="n">
-        <v>17.32753</v>
+        <v>17.27368</v>
       </c>
       <c r="E6" t="n">
-        <v>17.88653</v>
+        <v>17.56419</v>
       </c>
       <c r="F6" t="n">
-        <v>45.88941</v>
+        <v>43.93805</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05276</v>
+        <v>0.05261</v>
       </c>
       <c r="H6" t="n">
-        <v>1.91902</v>
+        <v>1.94483</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.90923</v>
+        <v>17.65564</v>
       </c>
       <c r="D7" t="n">
-        <v>17.48966</v>
+        <v>17.3996</v>
       </c>
       <c r="E7" t="n">
-        <v>17.53185</v>
+        <v>17.58272</v>
       </c>
       <c r="F7" t="n">
-        <v>44.64225</v>
+        <v>45.98174</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05371</v>
+        <v>0.05324</v>
       </c>
       <c r="H7" t="n">
-        <v>1.91809</v>
+        <v>1.89179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.475</v>
+        <v>17.78424</v>
       </c>
       <c r="D8" t="n">
-        <v>17.40429</v>
+        <v>17.33638</v>
       </c>
       <c r="E8" t="n">
-        <v>17.46686</v>
+        <v>17.61178</v>
       </c>
       <c r="F8" t="n">
-        <v>44.77909</v>
+        <v>44.24322</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05325</v>
+        <v>0.05378</v>
       </c>
       <c r="H8" t="n">
-        <v>1.92124</v>
+        <v>1.91602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.51911</v>
+        <v>17.81513</v>
       </c>
       <c r="D9" t="n">
-        <v>17.64066</v>
+        <v>17.59354</v>
       </c>
       <c r="E9" t="n">
-        <v>17.47331</v>
+        <v>17.81246</v>
       </c>
       <c r="F9" t="n">
-        <v>44.5462</v>
+        <v>44.60989</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05303</v>
+        <v>0.05326</v>
       </c>
       <c r="H9" t="n">
-        <v>1.93068</v>
+        <v>1.96106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.83766</v>
+        <v>17.93444</v>
       </c>
       <c r="D10" t="n">
-        <v>17.89524</v>
+        <v>17.22466</v>
       </c>
       <c r="E10" t="n">
-        <v>17.51578</v>
+        <v>17.90337</v>
       </c>
       <c r="F10" t="n">
-        <v>44.24485</v>
+        <v>45.00602</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05284</v>
+        <v>0.05286</v>
       </c>
       <c r="H10" t="n">
-        <v>1.93149</v>
+        <v>1.92379</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>17.97319</v>
-      </c>
-      <c r="D11" t="n">
-        <v>17.23257</v>
-      </c>
-      <c r="E11" t="n">
-        <v>17.4406</v>
-      </c>
-      <c r="F11" t="n">
-        <v>45.0574</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.05431</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.87663</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pad Pos 2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>18.20876</v>
+      </c>
+      <c r="D12" t="n">
+        <v>17.71932</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.96452</v>
+      </c>
+      <c r="F12" t="n">
+        <v>44.9864</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05274</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.92381</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>via 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.65097</v>
+        <v>17.84235</v>
       </c>
       <c r="D13" t="n">
-        <v>1.16952</v>
+        <v>17.68907</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.70166</v>
+      </c>
+      <c r="F13" t="n">
+        <v>44.32204</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05367</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.95751</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.65074</v>
+        <v>17.96426</v>
       </c>
       <c r="D14" t="n">
-        <v>1.16253</v>
+        <v>17.60013</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.62464</v>
+      </c>
+      <c r="F14" t="n">
+        <v>44.93873</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05392</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.96123</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6542</v>
+        <v>18.11742</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1611</v>
+        <v>17.57111</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.6309</v>
+      </c>
+      <c r="F15" t="n">
+        <v>44.34467</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05387</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.94009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.65839</v>
+        <v>17.90458</v>
       </c>
       <c r="D16" t="n">
-        <v>1.18204</v>
+        <v>17.59157</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.61529</v>
+      </c>
+      <c r="F16" t="n">
+        <v>44.95056</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05357</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.93455</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.63818</v>
+        <v>17.908</v>
       </c>
       <c r="D17" t="n">
-        <v>1.16898</v>
+        <v>17.44396</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.46164</v>
+      </c>
+      <c r="F17" t="n">
+        <v>45.18348</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05394</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.89938</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.63131</v>
+        <v>17.78596</v>
       </c>
       <c r="D18" t="n">
-        <v>1.17846</v>
+        <v>17.55455</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.7136</v>
+      </c>
+      <c r="F18" t="n">
+        <v>45.34359</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05353</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.91593</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.64295</v>
+        <v>17.7567</v>
       </c>
       <c r="D19" t="n">
-        <v>1.16933</v>
+        <v>17.32089</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.74033</v>
+      </c>
+      <c r="F19" t="n">
+        <v>44.55326</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05251</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.92935</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17.84341</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17.68934</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.83441</v>
+      </c>
+      <c r="F20" t="n">
+        <v>46.05305</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05406</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.94014</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad Pos 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>16.70814</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16.49419</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.54831</v>
+      </c>
+      <c r="F22" t="n">
+        <v>270.00946</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>16.70157</v>
+      </c>
+      <c r="D23" t="n">
+        <v>16.46397</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.67916</v>
+      </c>
+      <c r="F23" t="n">
+        <v>271.56644</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>16.87611</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16.5248</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.53677</v>
+      </c>
+      <c r="F24" t="n">
+        <v>267.38434</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>16.6891</v>
+      </c>
+      <c r="D25" t="n">
+        <v>16.54903</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.58194</v>
+      </c>
+      <c r="F25" t="n">
+        <v>268.86297</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>16.83505</v>
+      </c>
+      <c r="D26" t="n">
+        <v>16.59319</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.67281</v>
+      </c>
+      <c r="F26" t="n">
+        <v>265.18287</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>16.54754</v>
+      </c>
+      <c r="D27" t="n">
+        <v>16.35767</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.47644</v>
+      </c>
+      <c r="F27" t="n">
+        <v>265.64981</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>16.799</v>
+      </c>
+      <c r="D28" t="n">
+        <v>16.35852</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.5434</v>
+      </c>
+      <c r="F28" t="n">
+        <v>271.82215</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>0.64319</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.14568</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="C29" t="n">
+        <v>16.67849</v>
+      </c>
+      <c r="D29" t="n">
+        <v>16.44664</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.51836</v>
+      </c>
+      <c r="F29" t="n">
+        <v>270.53011</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>0.65421</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.18025</v>
+      <c r="C30" t="n">
+        <v>16.57821</v>
+      </c>
+      <c r="D30" t="n">
+        <v>16.41182</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.46351</v>
+      </c>
+      <c r="F30" t="n">
+        <v>270.23255</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace Pos 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>17.80036</v>
+      </c>
+      <c r="D32" t="n">
+        <v>17.0711</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17.50849</v>
+      </c>
+      <c r="F32" t="n">
+        <v>23.02552</v>
+      </c>
+      <c r="G32" t="n">
+        <v>36.58236</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>17.53505</v>
+      </c>
+      <c r="D33" t="n">
+        <v>16.8428</v>
+      </c>
+      <c r="E33" t="n">
+        <v>17.38838</v>
+      </c>
+      <c r="F33" t="n">
+        <v>22.84069</v>
+      </c>
+      <c r="G33" t="n">
+        <v>36.44257</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>17.35885</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.82218</v>
+      </c>
+      <c r="E34" t="n">
+        <v>17.21557</v>
+      </c>
+      <c r="F34" t="n">
+        <v>23.15261</v>
+      </c>
+      <c r="G34" t="n">
+        <v>35.25834</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.86014</v>
+      </c>
+      <c r="D35" t="n">
+        <v>17.03047</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.45274</v>
+      </c>
+      <c r="F35" t="n">
+        <v>22.81951</v>
+      </c>
+      <c r="G35" t="n">
+        <v>35.98291</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>17.37848</v>
+      </c>
+      <c r="D36" t="n">
+        <v>17.13524</v>
+      </c>
+      <c r="E36" t="n">
+        <v>17.29533</v>
+      </c>
+      <c r="F36" t="n">
+        <v>23.17449</v>
+      </c>
+      <c r="G36" t="n">
+        <v>36.39866</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>17.86596</v>
+      </c>
+      <c r="D37" t="n">
+        <v>16.4612</v>
+      </c>
+      <c r="E37" t="n">
+        <v>17.01912</v>
+      </c>
+      <c r="F37" t="n">
+        <v>22.59371</v>
+      </c>
+      <c r="G37" t="n">
+        <v>35.95771</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>17.54897</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.64994</v>
+      </c>
+      <c r="E38" t="n">
+        <v>17.27158</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22.48786</v>
+      </c>
+      <c r="G38" t="n">
+        <v>36.37887</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>17.96006</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.96351</v>
+      </c>
+      <c r="E39" t="n">
+        <v>17.26346</v>
+      </c>
+      <c r="F39" t="n">
+        <v>22.65436</v>
+      </c>
+      <c r="G39" t="n">
+        <v>36.58749</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>17.70458</v>
+      </c>
+      <c r="D40" t="n">
+        <v>16.82504</v>
+      </c>
+      <c r="E40" t="n">
+        <v>17.1671</v>
+      </c>
+      <c r="F40" t="n">
+        <v>23.72462</v>
+      </c>
+      <c r="G40" t="n">
+        <v>36.28694</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Via Pos 1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.63107</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.18231</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6501400000000001</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.14941</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.6397699999999999</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.1634</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.17284</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.66398</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.15885</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.65067</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.18849</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.65019</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.16309</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.64637</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.18045</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.64271</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.18772</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Landing Pad 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>17.99677</v>
+      </c>
+      <c r="D52" t="n">
+        <v>17.32561</v>
+      </c>
+      <c r="E52" t="n">
+        <v>17.7126</v>
+      </c>
+      <c r="F52" t="n">
+        <v>45.12345</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>17.61729</v>
+      </c>
+      <c r="D53" t="n">
+        <v>17.56299</v>
+      </c>
+      <c r="E53" t="n">
+        <v>17.60827</v>
+      </c>
+      <c r="F53" t="n">
+        <v>45.89736</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>17.93162</v>
+      </c>
+      <c r="D54" t="n">
+        <v>17.59486</v>
+      </c>
+      <c r="E54" t="n">
+        <v>17.84044</v>
+      </c>
+      <c r="F54" t="n">
+        <v>45.0095</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>17.90445</v>
+      </c>
+      <c r="D55" t="n">
+        <v>17.64979</v>
+      </c>
+      <c r="E55" t="n">
+        <v>17.81038</v>
+      </c>
+      <c r="F55" t="n">
+        <v>44.44941</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>17.98971</v>
+      </c>
+      <c r="D56" t="n">
+        <v>17.51239</v>
+      </c>
+      <c r="E56" t="n">
+        <v>17.86124</v>
+      </c>
+      <c r="F56" t="n">
+        <v>44.62426</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>17.75889</v>
+      </c>
+      <c r="D57" t="n">
+        <v>17.4607</v>
+      </c>
+      <c r="E57" t="n">
+        <v>17.69321</v>
+      </c>
+      <c r="F57" t="n">
+        <v>44.16428</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>17.80784</v>
+      </c>
+      <c r="D58" t="n">
+        <v>17.4739</v>
+      </c>
+      <c r="E58" t="n">
+        <v>17.68749</v>
+      </c>
+      <c r="F58" t="n">
+        <v>44.58884</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>17.76285</v>
+      </c>
+      <c r="D59" t="n">
+        <v>17.42854</v>
+      </c>
+      <c r="E59" t="n">
+        <v>17.73844</v>
+      </c>
+      <c r="F59" t="n">
+        <v>45.50949</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>18.12928</v>
+      </c>
+      <c r="D60" t="n">
+        <v>17.65546</v>
+      </c>
+      <c r="E60" t="n">
+        <v>17.7621</v>
+      </c>
+      <c r="F60" t="n">
+        <v>44.97511</v>
       </c>
     </row>
   </sheetData>
